--- a/backend/data/financials_by_company/1KGX.MI.xlsx
+++ b/backend/data/financials_by_company/1KGX.MI.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV5"/>
+  <dimension ref="A1:AV6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -662,55 +662,55 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>2655400</v>
+        <v>2192400</v>
       </c>
       <c r="C2" t="n">
-        <v>0.374</v>
+        <v>0.252</v>
       </c>
       <c r="D2" t="n">
-        <v>2086300000</v>
+        <v>1797800000</v>
       </c>
       <c r="E2" t="n">
-        <v>7100000</v>
+        <v>8700000</v>
       </c>
       <c r="F2" t="n">
-        <v>7100000</v>
+        <v>8700000</v>
       </c>
       <c r="G2" t="n">
-        <v>360300000</v>
+        <v>568300000</v>
       </c>
       <c r="H2" t="n">
-        <v>1139200000</v>
+        <v>940900000</v>
       </c>
       <c r="I2" t="n">
-        <v>8409700000</v>
+        <v>7770700000</v>
       </c>
       <c r="J2" t="n">
-        <v>2093400000</v>
+        <v>1806500000</v>
       </c>
       <c r="K2" t="n">
-        <v>954200000</v>
+        <v>865600000</v>
       </c>
       <c r="L2" t="n">
-        <v>-206700000</v>
+        <v>-28000000</v>
       </c>
       <c r="M2" t="n">
-        <v>364400000</v>
+        <v>105900000</v>
       </c>
       <c r="N2" t="n">
-        <v>157700000</v>
+        <v>77900000</v>
       </c>
       <c r="O2" t="n">
-        <v>355855400</v>
+        <v>561792400</v>
       </c>
       <c r="P2" t="n">
-        <v>360300000</v>
+        <v>568300000</v>
       </c>
       <c r="Q2" t="n">
-        <v>10705600000</v>
+        <v>9526800000</v>
       </c>
       <c r="R2" t="n">
         <v>131100000</v>
@@ -719,144 +719,144 @@
         <v>131100000</v>
       </c>
       <c r="T2" t="n">
-        <v>2.75</v>
+        <v>4.33</v>
       </c>
       <c r="U2" t="n">
-        <v>2.75</v>
+        <v>4.34</v>
       </c>
       <c r="V2" t="n">
-        <v>360300000</v>
+        <v>568300000</v>
       </c>
       <c r="W2" t="n">
-        <v>360300000</v>
+        <v>568300000</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>360300000</v>
+        <v>568300000</v>
       </c>
       <c r="Z2" t="n">
-        <v>-8900000</v>
+        <v>300000</v>
       </c>
       <c r="AA2" t="n">
-        <v>369200000</v>
+        <v>568000000</v>
       </c>
       <c r="AB2" t="n">
-        <v>369300000</v>
+        <v>568000000</v>
       </c>
       <c r="AC2" t="n">
-        <v>220500000</v>
+        <v>191700000</v>
       </c>
       <c r="AD2" t="n">
-        <v>589800000</v>
+        <v>759700000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-10300000</v>
+        <v>15800000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-24400000</v>
+        <v>3800000</v>
       </c>
       <c r="AG2" t="n">
-        <v>-5600000</v>
+        <v>-6100000</v>
       </c>
       <c r="AH2" t="n">
-        <v>30000000</v>
+        <v>2300000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-206700000</v>
+        <v>-28000000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>364400000</v>
+        <v>105900000</v>
       </c>
       <c r="AK2" t="n">
-        <v>157700000</v>
+        <v>77900000</v>
       </c>
       <c r="AL2" t="n">
-        <v>797600000</v>
+        <v>767500000</v>
       </c>
       <c r="AM2" t="n">
-        <v>2295900000</v>
+        <v>1756100000</v>
       </c>
       <c r="AN2" t="n">
-        <v>-5100000</v>
+        <v>-3800000</v>
       </c>
       <c r="AO2" t="n">
-        <v>259600000</v>
+        <v>174700000</v>
       </c>
       <c r="AP2" t="n">
-        <v>2041400000</v>
+        <v>1585200000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1206500000</v>
+        <v>970200000</v>
       </c>
       <c r="AR2" t="n">
-        <v>834900000</v>
+        <v>615000000</v>
       </c>
       <c r="AS2" t="n">
-        <v>3093500000</v>
+        <v>2523600000</v>
       </c>
       <c r="AT2" t="n">
-        <v>8409700000</v>
+        <v>7770700000</v>
       </c>
       <c r="AU2" t="n">
-        <v>11503200000</v>
+        <v>10294300000</v>
       </c>
       <c r="AV2" t="n">
-        <v>11503200000</v>
+        <v>10294300000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>4613600</v>
+        <v>4427000</v>
       </c>
       <c r="C3" t="n">
-        <v>0.316</v>
+        <v>0.233</v>
       </c>
       <c r="D3" t="n">
-        <v>1802800000</v>
+        <v>1296600000</v>
       </c>
       <c r="E3" t="n">
-        <v>14600000</v>
+        <v>19000000</v>
       </c>
       <c r="F3" t="n">
-        <v>14600000</v>
+        <v>19000000</v>
       </c>
       <c r="G3" t="n">
-        <v>305800000</v>
+        <v>98000000</v>
       </c>
       <c r="H3" t="n">
-        <v>1053000000</v>
+        <v>1033500000</v>
       </c>
       <c r="I3" t="n">
-        <v>8652500000</v>
+        <v>9011500000</v>
       </c>
       <c r="J3" t="n">
-        <v>1817400000</v>
+        <v>1315600000</v>
       </c>
       <c r="K3" t="n">
-        <v>764400000</v>
+        <v>282100000</v>
       </c>
       <c r="L3" t="n">
-        <v>-186200000</v>
+        <v>-42200000</v>
       </c>
       <c r="M3" t="n">
-        <v>304600000</v>
+        <v>144100000</v>
       </c>
       <c r="N3" t="n">
-        <v>118400000</v>
+        <v>101900000</v>
       </c>
       <c r="O3" t="n">
-        <v>295813600</v>
+        <v>83427000</v>
       </c>
       <c r="P3" t="n">
-        <v>305800000</v>
+        <v>98000000</v>
       </c>
       <c r="Q3" t="n">
-        <v>10783600000</v>
+        <v>10980700000</v>
       </c>
       <c r="R3" t="n">
         <v>131100000</v>
@@ -865,144 +865,144 @@
         <v>131100000</v>
       </c>
       <c r="T3" t="n">
-        <v>2.33</v>
+        <v>0.75</v>
       </c>
       <c r="U3" t="n">
-        <v>2.33</v>
+        <v>0.75</v>
       </c>
       <c r="V3" t="n">
-        <v>305800000</v>
+        <v>98000000</v>
       </c>
       <c r="W3" t="n">
-        <v>305800000</v>
+        <v>98000000</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>305800000</v>
+        <v>98000000</v>
       </c>
       <c r="Z3" t="n">
-        <v>-8600000</v>
+        <v>-7800000</v>
       </c>
       <c r="AA3" t="n">
-        <v>314400000</v>
+        <v>105800000</v>
       </c>
       <c r="AB3" t="n">
-        <v>314400000</v>
+        <v>105800000</v>
       </c>
       <c r="AC3" t="n">
-        <v>145400000</v>
+        <v>32200000</v>
       </c>
       <c r="AD3" t="n">
-        <v>459800000</v>
+        <v>138000000</v>
       </c>
       <c r="AE3" t="n">
-        <v>6500000</v>
+        <v>14800000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-700000</v>
+        <v>-15500000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-6000000</v>
+        <v>-4700000</v>
       </c>
       <c r="AH3" t="n">
-        <v>6700000</v>
+        <v>20200000</v>
       </c>
       <c r="AI3" t="n">
-        <v>-186200000</v>
+        <v>-42200000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>304600000</v>
+        <v>144100000</v>
       </c>
       <c r="AK3" t="n">
-        <v>118400000</v>
+        <v>101900000</v>
       </c>
       <c r="AL3" t="n">
-        <v>650100000</v>
+        <v>154800000</v>
       </c>
       <c r="AM3" t="n">
-        <v>2131100000</v>
+        <v>1969200000</v>
       </c>
       <c r="AN3" t="n">
-        <v>-8200000</v>
+        <v>-8700000</v>
       </c>
       <c r="AO3" t="n">
-        <v>235100000</v>
+        <v>203300000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1904200000</v>
+        <v>1774600000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1143300000</v>
+        <v>1118600000</v>
       </c>
       <c r="AR3" t="n">
-        <v>760900000</v>
+        <v>656000000</v>
       </c>
       <c r="AS3" t="n">
-        <v>2781200000</v>
+        <v>2124000000</v>
       </c>
       <c r="AT3" t="n">
-        <v>8652500000</v>
+        <v>9011500000</v>
       </c>
       <c r="AU3" t="n">
-        <v>11433700000</v>
+        <v>11135600000</v>
       </c>
       <c r="AV3" t="n">
-        <v>11433700000</v>
+        <v>11135600000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>4427000</v>
+        <v>4613600</v>
       </c>
       <c r="C4" t="n">
-        <v>0.233</v>
+        <v>0.316</v>
       </c>
       <c r="D4" t="n">
-        <v>1296600000</v>
+        <v>1802800000</v>
       </c>
       <c r="E4" t="n">
-        <v>19000000</v>
+        <v>14600000</v>
       </c>
       <c r="F4" t="n">
-        <v>19000000</v>
+        <v>14600000</v>
       </c>
       <c r="G4" t="n">
-        <v>98000000</v>
+        <v>305800000</v>
       </c>
       <c r="H4" t="n">
-        <v>1033500000</v>
+        <v>1053000000</v>
       </c>
       <c r="I4" t="n">
-        <v>9011500000</v>
+        <v>8652500000</v>
       </c>
       <c r="J4" t="n">
-        <v>1315600000</v>
+        <v>1817400000</v>
       </c>
       <c r="K4" t="n">
-        <v>282100000</v>
+        <v>764400000</v>
       </c>
       <c r="L4" t="n">
-        <v>-42200000</v>
+        <v>-186200000</v>
       </c>
       <c r="M4" t="n">
-        <v>144100000</v>
+        <v>304600000</v>
       </c>
       <c r="N4" t="n">
-        <v>101900000</v>
+        <v>118400000</v>
       </c>
       <c r="O4" t="n">
-        <v>83427000</v>
+        <v>295813600</v>
       </c>
       <c r="P4" t="n">
-        <v>98000000</v>
+        <v>305800000</v>
       </c>
       <c r="Q4" t="n">
-        <v>10980700000</v>
+        <v>10783600000</v>
       </c>
       <c r="R4" t="n">
         <v>131100000</v>
@@ -1011,144 +1011,144 @@
         <v>131100000</v>
       </c>
       <c r="T4" t="n">
-        <v>0.75</v>
+        <v>2.33</v>
       </c>
       <c r="U4" t="n">
-        <v>0.75</v>
+        <v>2.33</v>
       </c>
       <c r="V4" t="n">
-        <v>98000000</v>
+        <v>305800000</v>
       </c>
       <c r="W4" t="n">
-        <v>98000000</v>
+        <v>305800000</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>98000000</v>
+        <v>305800000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-7800000</v>
+        <v>-8600000</v>
       </c>
       <c r="AA4" t="n">
-        <v>105800000</v>
+        <v>314400000</v>
       </c>
       <c r="AB4" t="n">
-        <v>105800000</v>
+        <v>314400000</v>
       </c>
       <c r="AC4" t="n">
-        <v>32200000</v>
+        <v>145400000</v>
       </c>
       <c r="AD4" t="n">
-        <v>138000000</v>
+        <v>459800000</v>
       </c>
       <c r="AE4" t="n">
-        <v>14800000</v>
+        <v>6500000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-15500000</v>
+        <v>-700000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-4700000</v>
+        <v>-6000000</v>
       </c>
       <c r="AH4" t="n">
-        <v>20200000</v>
+        <v>6700000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-42200000</v>
+        <v>-186200000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>144100000</v>
+        <v>304600000</v>
       </c>
       <c r="AK4" t="n">
-        <v>101900000</v>
+        <v>118400000</v>
       </c>
       <c r="AL4" t="n">
-        <v>154800000</v>
+        <v>650100000</v>
       </c>
       <c r="AM4" t="n">
-        <v>1969200000</v>
+        <v>2131100000</v>
       </c>
       <c r="AN4" t="n">
-        <v>-8700000</v>
+        <v>-8200000</v>
       </c>
       <c r="AO4" t="n">
-        <v>203300000</v>
+        <v>235100000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1774600000</v>
+        <v>1904200000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>1118600000</v>
+        <v>1143300000</v>
       </c>
       <c r="AR4" t="n">
-        <v>656000000</v>
+        <v>760900000</v>
       </c>
       <c r="AS4" t="n">
-        <v>2124000000</v>
+        <v>2781200000</v>
       </c>
       <c r="AT4" t="n">
-        <v>9011500000</v>
+        <v>8652500000</v>
       </c>
       <c r="AU4" t="n">
-        <v>11135600000</v>
+        <v>11433700000</v>
       </c>
       <c r="AV4" t="n">
-        <v>11135600000</v>
+        <v>11433700000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>2192400</v>
+        <v>2654374.364191</v>
       </c>
       <c r="C5" t="n">
-        <v>0.252</v>
+        <v>0.373856</v>
       </c>
       <c r="D5" t="n">
-        <v>1797800000</v>
+        <v>2086300000</v>
       </c>
       <c r="E5" t="n">
-        <v>8700000</v>
+        <v>7100000</v>
       </c>
       <c r="F5" t="n">
-        <v>8700000</v>
+        <v>7100000</v>
       </c>
       <c r="G5" t="n">
-        <v>568300000</v>
+        <v>360300000</v>
       </c>
       <c r="H5" t="n">
-        <v>940900000</v>
+        <v>1139200000</v>
       </c>
       <c r="I5" t="n">
-        <v>7770700000</v>
+        <v>8409700000</v>
       </c>
       <c r="J5" t="n">
-        <v>1806500000</v>
+        <v>2093400000</v>
       </c>
       <c r="K5" t="n">
-        <v>865600000</v>
+        <v>954200000</v>
       </c>
       <c r="L5" t="n">
-        <v>-28000000</v>
+        <v>-206700000</v>
       </c>
       <c r="M5" t="n">
-        <v>105900000</v>
+        <v>364400000</v>
       </c>
       <c r="N5" t="n">
-        <v>77900000</v>
+        <v>157700000</v>
       </c>
       <c r="O5" t="n">
-        <v>561792400</v>
+        <v>355854374.364191</v>
       </c>
       <c r="P5" t="n">
-        <v>568300000</v>
+        <v>360300000</v>
       </c>
       <c r="Q5" t="n">
-        <v>9526800000</v>
+        <v>10705600000</v>
       </c>
       <c r="R5" t="n">
         <v>131100000</v>
@@ -1157,91 +1157,237 @@
         <v>131100000</v>
       </c>
       <c r="T5" t="n">
-        <v>4.33</v>
+        <v>2.75</v>
       </c>
       <c r="U5" t="n">
-        <v>4.34</v>
+        <v>2.75</v>
       </c>
       <c r="V5" t="n">
-        <v>568300000</v>
+        <v>360300000</v>
       </c>
       <c r="W5" t="n">
-        <v>568300000</v>
+        <v>360300000</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>568300000</v>
+        <v>360300000</v>
       </c>
       <c r="Z5" t="n">
-        <v>300000</v>
+        <v>-8900000</v>
       </c>
       <c r="AA5" t="n">
-        <v>568000000</v>
+        <v>369200000</v>
       </c>
       <c r="AB5" t="n">
-        <v>568000000</v>
+        <v>369300000</v>
       </c>
       <c r="AC5" t="n">
-        <v>191700000</v>
+        <v>220500000</v>
       </c>
       <c r="AD5" t="n">
-        <v>759700000</v>
+        <v>589800000</v>
       </c>
       <c r="AE5" t="n">
-        <v>15800000</v>
+        <v>-10300000</v>
       </c>
       <c r="AF5" t="n">
-        <v>3800000</v>
+        <v>-24400000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-6100000</v>
+        <v>-5600000</v>
       </c>
       <c r="AH5" t="n">
-        <v>2300000</v>
+        <v>30000000</v>
       </c>
       <c r="AI5" t="n">
-        <v>-28000000</v>
+        <v>-206700000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>105900000</v>
+        <v>364400000</v>
       </c>
       <c r="AK5" t="n">
-        <v>77900000</v>
+        <v>157700000</v>
       </c>
       <c r="AL5" t="n">
-        <v>767500000</v>
+        <v>797600000</v>
       </c>
       <c r="AM5" t="n">
-        <v>1756100000</v>
+        <v>2295900000</v>
       </c>
       <c r="AN5" t="n">
-        <v>-3800000</v>
+        <v>-5100000</v>
       </c>
       <c r="AO5" t="n">
-        <v>174700000</v>
+        <v>259600000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1585200000</v>
+        <v>2041400000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>970200000</v>
+        <v>1206500000</v>
       </c>
       <c r="AR5" t="n">
-        <v>615000000</v>
+        <v>834900000</v>
       </c>
       <c r="AS5" t="n">
-        <v>2523600000</v>
+        <v>3093500000</v>
       </c>
       <c r="AT5" t="n">
-        <v>7770700000</v>
+        <v>8409700000</v>
       </c>
       <c r="AU5" t="n">
-        <v>10294300000</v>
+        <v>11503200000</v>
       </c>
       <c r="AV5" t="n">
-        <v>10294300000</v>
+        <v>11503200000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-8598868.458273999</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.319661</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1921900000</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-26900000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-26900000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>230100000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1199700000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>8347000000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>1895000000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>695300000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-148200000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>341800000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>193600000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>248401131.541726</v>
+      </c>
+      <c r="P6" t="n">
+        <v>230100000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>10799800000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>131100000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>131100000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V6" t="n">
+        <v>230100000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>230100000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>230100000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>-10400000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>240500000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>240500000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>113000000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>353500000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>7300000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>-30800000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-13500000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>44300000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>-148200000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>341800000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>193600000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>497400000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>2452800000</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>-2800000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>259400000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>2196200000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>1283400000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>912800000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>2950200000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>8347000000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>11297200000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>11297200000</v>
       </c>
     </row>
   </sheetData>
@@ -1255,7 +1401,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CF5"/>
+  <dimension ref="A1:CF6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1677,261 +1823,101 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>73876</v>
-      </c>
-      <c r="C2" t="n">
-        <v>131124771</v>
-      </c>
-      <c r="D2" t="n">
-        <v>131198647</v>
-      </c>
-      <c r="E2" t="n">
-        <v>884100000</v>
-      </c>
-      <c r="F2" t="n">
-        <v>7662400000</v>
-      </c>
-      <c r="G2" t="n">
-        <v>374600000</v>
-      </c>
-      <c r="H2" t="n">
-        <v>7860000000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>58800000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>374600000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>5991800000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>6189400000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>7191200000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>6207100000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>17700000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>6189400000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>2135700000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>3826700000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>131100000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>131100000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>12598300000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>7088100000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>-100000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>34900000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>751800000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>200600000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>446700000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>5433800000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>4432000000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1001800000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>213100000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>5510200000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>-100000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>2228600000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>1559800000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>668800000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>526300000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>269400000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>1382100000</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>11200000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>210500000</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>1160400000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>18805400000</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>13236400000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="inlineStr"/>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr"/>
+      <c r="AQ2" t="inlineStr"/>
+      <c r="AR2" t="inlineStr"/>
       <c r="AS2" t="n">
-        <v>100000</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>80600000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>489300000</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>17600000</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>176600000</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>176600000</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>130100000</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>110300000</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>19800000</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>5814800000</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>2166600000</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>3648200000</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>4422800000</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>-3156800000</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>7579600000</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>218400000</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>5404500000</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>1025600000</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>931100000</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>5569000000</v>
-      </c>
+        <v>200000</v>
+      </c>
+      <c r="AT2" t="inlineStr"/>
+      <c r="AU2" t="inlineStr"/>
+      <c r="AV2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr"/>
+      <c r="AX2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
+      <c r="BA2" t="inlineStr"/>
+      <c r="BB2" t="inlineStr"/>
+      <c r="BC2" t="inlineStr"/>
+      <c r="BD2" t="inlineStr"/>
+      <c r="BE2" t="inlineStr"/>
+      <c r="BF2" t="inlineStr"/>
+      <c r="BG2" t="inlineStr"/>
+      <c r="BH2" t="inlineStr"/>
+      <c r="BI2" t="inlineStr"/>
+      <c r="BJ2" t="inlineStr"/>
+      <c r="BK2" t="inlineStr"/>
+      <c r="BL2" t="inlineStr"/>
+      <c r="BM2" t="inlineStr"/>
       <c r="BN2" t="n">
-        <v>-200000</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>12700000</v>
-      </c>
+        <v>400000</v>
+      </c>
+      <c r="BO2" t="inlineStr"/>
       <c r="BP2" t="n">
         <v>0</v>
       </c>
-      <c r="BQ2" t="n">
-        <v>82600000</v>
-      </c>
-      <c r="BR2" t="n">
-        <v>500000</v>
-      </c>
-      <c r="BS2" t="n">
-        <v>54100000</v>
-      </c>
-      <c r="BT2" t="n">
-        <v>1694600000</v>
-      </c>
-      <c r="BU2" t="n">
-        <v>945700000</v>
-      </c>
-      <c r="BV2" t="n">
-        <v>294300000</v>
-      </c>
-      <c r="BW2" t="n">
-        <v>454600000</v>
-      </c>
-      <c r="BX2" t="n">
-        <v>288300000</v>
-      </c>
-      <c r="BY2" t="n">
-        <v>177200000</v>
-      </c>
-      <c r="BZ2" t="n">
-        <v>1695600000</v>
-      </c>
-      <c r="CA2" t="n">
-        <v>-90100000</v>
-      </c>
-      <c r="CB2" t="n">
-        <v>1785700000</v>
-      </c>
-      <c r="CC2" t="n">
-        <v>839800000</v>
-      </c>
-      <c r="CD2" t="n">
-        <v>53300000</v>
-      </c>
-      <c r="CE2" t="n">
-        <v>786500000</v>
-      </c>
-      <c r="CF2" t="n">
-        <v>786500000</v>
-      </c>
+      <c r="BQ2" t="inlineStr"/>
+      <c r="BR2" t="inlineStr"/>
+      <c r="BS2" t="inlineStr"/>
+      <c r="BT2" t="inlineStr"/>
+      <c r="BU2" t="inlineStr"/>
+      <c r="BV2" t="inlineStr"/>
+      <c r="BW2" t="inlineStr"/>
+      <c r="BX2" t="inlineStr"/>
+      <c r="BY2" t="inlineStr"/>
+      <c r="BZ2" t="inlineStr"/>
+      <c r="CA2" t="inlineStr"/>
+      <c r="CB2" t="inlineStr"/>
+      <c r="CC2" t="inlineStr"/>
+      <c r="CD2" t="inlineStr"/>
+      <c r="CE2" t="inlineStr"/>
+      <c r="CF2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>73876</v>
@@ -1943,43 +1929,43 @@
         <v>131198647</v>
       </c>
       <c r="E3" t="n">
-        <v>1156700000</v>
+        <v>1329100000</v>
       </c>
       <c r="F3" t="n">
-        <v>6578300000</v>
+        <v>5979000000</v>
       </c>
       <c r="G3" t="n">
-        <v>101800000</v>
+        <v>-172900000</v>
       </c>
       <c r="H3" t="n">
-        <v>7233200000</v>
+        <v>7243900000</v>
       </c>
       <c r="I3" t="n">
-        <v>271500000</v>
+        <v>235900000</v>
       </c>
       <c r="J3" t="n">
-        <v>101800000</v>
+        <v>-172900000</v>
       </c>
       <c r="K3" t="n">
-        <v>5111900000</v>
+        <v>4343700000</v>
       </c>
       <c r="L3" t="n">
-        <v>5766800000</v>
+        <v>5608600000</v>
       </c>
       <c r="M3" t="n">
-        <v>7055500000</v>
+        <v>6939700000</v>
       </c>
       <c r="N3" t="n">
-        <v>5772700000</v>
+        <v>5607700000</v>
       </c>
       <c r="O3" t="n">
-        <v>5900000</v>
+        <v>-900000</v>
       </c>
       <c r="P3" t="n">
-        <v>5766800000</v>
+        <v>5608600000</v>
       </c>
       <c r="Q3" t="n">
-        <v>1867300000</v>
+        <v>1600500000</v>
       </c>
       <c r="R3" t="n">
         <v>3826700000</v>
@@ -1991,199 +1977,199 @@
         <v>131100000</v>
       </c>
       <c r="U3" t="n">
-        <v>11615700000</v>
+        <v>10991700000</v>
       </c>
       <c r="V3" t="n">
-        <v>6663900000</v>
+        <v>6040900000</v>
       </c>
       <c r="W3" t="n">
+        <v>200000</v>
+      </c>
+      <c r="X3" t="n">
+        <v>5400000</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>718200000</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>180600000</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>492800000</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>4466400000</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>3135300000</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1331100000</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>140800000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>4950800000</v>
+      </c>
+      <c r="AG3" t="n">
         <v>-100000</v>
       </c>
-      <c r="X3" t="n">
-        <v>33600000</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>780000000</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>173400000</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>448900000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>5030000000</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>3741300000</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1288700000</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>173700000</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>4951800000</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>-200000</v>
-      </c>
       <c r="AH3" t="n">
-        <v>1548300000</v>
+        <v>1512600000</v>
       </c>
       <c r="AI3" t="n">
-        <v>1370600000</v>
+        <v>1208400000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>177700000</v>
+        <v>304200000</v>
       </c>
       <c r="AK3" t="n">
-        <v>506500000</v>
+        <v>409600000</v>
       </c>
       <c r="AL3" t="n">
-        <v>278600000</v>
+        <v>229400000</v>
       </c>
       <c r="AM3" t="n">
-        <v>1426200000</v>
+        <v>1312400000</v>
       </c>
       <c r="AN3" t="n">
-        <v>11700000</v>
+        <v>6800000</v>
       </c>
       <c r="AO3" t="n">
-        <v>220500000</v>
+        <v>181300000</v>
       </c>
       <c r="AP3" t="n">
-        <v>1194000000</v>
+        <v>1124300000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>17388400000</v>
+        <v>16599400000</v>
       </c>
       <c r="AR3" t="n">
-        <v>12165100000</v>
-      </c>
-      <c r="AS3" t="inlineStr"/>
+        <v>11412600000</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>100000</v>
+      </c>
       <c r="AT3" t="n">
-        <v>100900000</v>
+        <v>94000000</v>
       </c>
       <c r="AU3" t="n">
-        <v>443200000</v>
+        <v>300800000</v>
       </c>
       <c r="AV3" t="n">
-        <v>36900000</v>
+        <v>78100000</v>
       </c>
       <c r="AW3" t="n">
-        <v>136200000</v>
+        <v>83300000</v>
       </c>
       <c r="AX3" t="n">
-        <v>136200000</v>
+        <v>83300000</v>
       </c>
       <c r="AY3" t="n">
-        <v>120400000</v>
+        <v>118500000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>103600000</v>
+        <v>94700000</v>
       </c>
       <c r="BA3" t="n">
-        <v>16800000</v>
+        <v>23800000</v>
       </c>
       <c r="BB3" t="n">
-        <v>5665000000</v>
+        <v>5781500000</v>
       </c>
       <c r="BC3" t="n">
-        <v>2106900000</v>
+        <v>2162100000</v>
       </c>
       <c r="BD3" t="n">
-        <v>3558100000</v>
+        <v>3619400000</v>
       </c>
       <c r="BE3" t="n">
-        <v>3942500000</v>
+        <v>3555000000</v>
       </c>
       <c r="BF3" t="n">
-        <v>-3289600000</v>
+        <v>-3200800000</v>
       </c>
       <c r="BG3" t="n">
-        <v>7232100000</v>
+        <v>6755800000</v>
       </c>
       <c r="BH3" t="n">
-        <v>188600000</v>
+        <v>143300000</v>
       </c>
       <c r="BI3" t="n">
-        <v>5252000000</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>895900000</v>
-      </c>
+        <v>4892200000</v>
+      </c>
+      <c r="BJ3" t="inlineStr"/>
       <c r="BK3" t="n">
-        <v>895600000</v>
+        <v>1720300000</v>
       </c>
       <c r="BL3" t="n">
         <v>0</v>
       </c>
       <c r="BM3" t="n">
-        <v>5223300000</v>
+        <v>5186700000</v>
       </c>
       <c r="BN3" t="n">
-        <v>-100000</v>
+        <v>1000000</v>
       </c>
       <c r="BO3" t="n">
-        <v>10200000</v>
+        <v>20500000</v>
       </c>
       <c r="BP3" t="n">
-        <v>55200000</v>
+        <v>27400000</v>
       </c>
       <c r="BQ3" t="n">
-        <v>60400000</v>
+        <v>48200000</v>
       </c>
       <c r="BR3" t="n">
-        <v>2100000</v>
+        <v>11900000</v>
       </c>
       <c r="BS3" t="n">
-        <v>73700000</v>
+        <v>62000000</v>
       </c>
       <c r="BT3" t="n">
-        <v>1743500000</v>
+        <v>1742600000</v>
       </c>
       <c r="BU3" t="n">
-        <v>959600000</v>
+        <v>890300000</v>
       </c>
       <c r="BV3" t="n">
-        <v>318100000</v>
+        <v>340100000</v>
       </c>
       <c r="BW3" t="n">
-        <v>465800000</v>
+        <v>512200000</v>
       </c>
       <c r="BX3" t="n">
-        <v>413800000</v>
+        <v>538900000</v>
       </c>
       <c r="BY3" t="n">
-        <v>141700000</v>
+        <v>191200000</v>
       </c>
       <c r="BZ3" t="n">
-        <v>1755800000</v>
+        <v>1667300000</v>
       </c>
       <c r="CA3" t="n">
-        <v>-81000000</v>
+        <v>-74700000</v>
       </c>
       <c r="CB3" t="n">
-        <v>1836800000</v>
+        <v>1742000000</v>
       </c>
       <c r="CC3" t="n">
-        <v>354500000</v>
+        <v>355900000</v>
       </c>
       <c r="CD3" t="n">
-        <v>44800000</v>
+        <v>49700000</v>
       </c>
       <c r="CE3" t="n">
-        <v>309700000</v>
+        <v>306200000</v>
       </c>
       <c r="CF3" t="n">
-        <v>309700000</v>
+        <v>306200000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>73876</v>
@@ -2195,43 +2181,43 @@
         <v>131198647</v>
       </c>
       <c r="E4" t="n">
-        <v>1329100000</v>
+        <v>1156700000</v>
       </c>
       <c r="F4" t="n">
-        <v>5979000000</v>
+        <v>6578300000</v>
       </c>
       <c r="G4" t="n">
-        <v>-172900000</v>
+        <v>101800000</v>
       </c>
       <c r="H4" t="n">
-        <v>7243900000</v>
+        <v>7233200000</v>
       </c>
       <c r="I4" t="n">
-        <v>235900000</v>
+        <v>271500000</v>
       </c>
       <c r="J4" t="n">
-        <v>-172900000</v>
+        <v>101800000</v>
       </c>
       <c r="K4" t="n">
-        <v>4343700000</v>
+        <v>5111900000</v>
       </c>
       <c r="L4" t="n">
-        <v>5608600000</v>
+        <v>5766800000</v>
       </c>
       <c r="M4" t="n">
-        <v>6939700000</v>
+        <v>7055500000</v>
       </c>
       <c r="N4" t="n">
-        <v>5607700000</v>
+        <v>5772700000</v>
       </c>
       <c r="O4" t="n">
-        <v>-900000</v>
+        <v>5900000</v>
       </c>
       <c r="P4" t="n">
-        <v>5608600000</v>
+        <v>5766800000</v>
       </c>
       <c r="Q4" t="n">
-        <v>1600500000</v>
+        <v>1867300000</v>
       </c>
       <c r="R4" t="n">
         <v>3826700000</v>
@@ -2243,250 +2229,250 @@
         <v>131100000</v>
       </c>
       <c r="U4" t="n">
-        <v>10991700000</v>
+        <v>11615700000</v>
       </c>
       <c r="V4" t="n">
-        <v>6040900000</v>
+        <v>6663900000</v>
       </c>
       <c r="W4" t="n">
-        <v>200000</v>
+        <v>-100000</v>
       </c>
       <c r="X4" t="n">
-        <v>5400000</v>
+        <v>33600000</v>
       </c>
       <c r="Y4" t="n">
-        <v>718200000</v>
+        <v>780000000</v>
       </c>
       <c r="Z4" t="n">
-        <v>180600000</v>
+        <v>173400000</v>
       </c>
       <c r="AA4" t="n">
-        <v>492800000</v>
+        <v>448900000</v>
       </c>
       <c r="AB4" t="n">
-        <v>4466400000</v>
+        <v>5030000000</v>
       </c>
       <c r="AC4" t="n">
-        <v>3135300000</v>
+        <v>3741300000</v>
       </c>
       <c r="AD4" t="n">
-        <v>1331100000</v>
+        <v>1288700000</v>
       </c>
       <c r="AE4" t="n">
-        <v>140800000</v>
+        <v>173700000</v>
       </c>
       <c r="AF4" t="n">
-        <v>4950800000</v>
+        <v>4951800000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-100000</v>
+        <v>-200000</v>
       </c>
       <c r="AH4" t="n">
-        <v>1512600000</v>
+        <v>1548300000</v>
       </c>
       <c r="AI4" t="n">
-        <v>1208400000</v>
+        <v>1370600000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>304200000</v>
+        <v>177700000</v>
       </c>
       <c r="AK4" t="n">
-        <v>409600000</v>
+        <v>506500000</v>
       </c>
       <c r="AL4" t="n">
-        <v>229400000</v>
+        <v>278600000</v>
       </c>
       <c r="AM4" t="n">
-        <v>1312400000</v>
+        <v>1426200000</v>
       </c>
       <c r="AN4" t="n">
-        <v>6800000</v>
+        <v>11700000</v>
       </c>
       <c r="AO4" t="n">
-        <v>181300000</v>
+        <v>220500000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1124300000</v>
+        <v>1194000000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>16599400000</v>
+        <v>17388400000</v>
       </c>
       <c r="AR4" t="n">
-        <v>11412600000</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>100000</v>
-      </c>
+        <v>12165100000</v>
+      </c>
+      <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
-        <v>94000000</v>
+        <v>100900000</v>
       </c>
       <c r="AU4" t="n">
-        <v>300800000</v>
+        <v>443200000</v>
       </c>
       <c r="AV4" t="n">
-        <v>78100000</v>
+        <v>36900000</v>
       </c>
       <c r="AW4" t="n">
-        <v>83300000</v>
+        <v>136200000</v>
       </c>
       <c r="AX4" t="n">
-        <v>83300000</v>
+        <v>136200000</v>
       </c>
       <c r="AY4" t="n">
-        <v>118500000</v>
+        <v>120400000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>94700000</v>
+        <v>103600000</v>
       </c>
       <c r="BA4" t="n">
-        <v>23800000</v>
+        <v>16800000</v>
       </c>
       <c r="BB4" t="n">
-        <v>5781500000</v>
+        <v>5665000000</v>
       </c>
       <c r="BC4" t="n">
-        <v>2162100000</v>
+        <v>2106900000</v>
       </c>
       <c r="BD4" t="n">
-        <v>3619400000</v>
+        <v>3558100000</v>
       </c>
       <c r="BE4" t="n">
-        <v>3555000000</v>
+        <v>3942500000</v>
       </c>
       <c r="BF4" t="n">
-        <v>-3200800000</v>
+        <v>-3289600000</v>
       </c>
       <c r="BG4" t="n">
-        <v>6755800000</v>
+        <v>7232100000</v>
       </c>
       <c r="BH4" t="n">
-        <v>143300000</v>
+        <v>188600000</v>
       </c>
       <c r="BI4" t="n">
-        <v>4892200000</v>
-      </c>
-      <c r="BJ4" t="inlineStr"/>
+        <v>5252000000</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>895900000</v>
+      </c>
       <c r="BK4" t="n">
-        <v>1720300000</v>
+        <v>895600000</v>
       </c>
       <c r="BL4" t="n">
         <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>5186700000</v>
+        <v>5223300000</v>
       </c>
       <c r="BN4" t="n">
-        <v>1000000</v>
+        <v>-100000</v>
       </c>
       <c r="BO4" t="n">
-        <v>20500000</v>
+        <v>10200000</v>
       </c>
       <c r="BP4" t="n">
-        <v>27400000</v>
+        <v>55200000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>48200000</v>
+        <v>60400000</v>
       </c>
       <c r="BR4" t="n">
-        <v>11900000</v>
+        <v>2100000</v>
       </c>
       <c r="BS4" t="n">
-        <v>62000000</v>
+        <v>73700000</v>
       </c>
       <c r="BT4" t="n">
-        <v>1742600000</v>
+        <v>1743500000</v>
       </c>
       <c r="BU4" t="n">
-        <v>890300000</v>
+        <v>959600000</v>
       </c>
       <c r="BV4" t="n">
-        <v>340100000</v>
+        <v>318100000</v>
       </c>
       <c r="BW4" t="n">
-        <v>512200000</v>
+        <v>465800000</v>
       </c>
       <c r="BX4" t="n">
-        <v>538900000</v>
+        <v>413800000</v>
       </c>
       <c r="BY4" t="n">
-        <v>191200000</v>
+        <v>141700000</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1667300000</v>
+        <v>1755800000</v>
       </c>
       <c r="CA4" t="n">
-        <v>-74700000</v>
+        <v>-81000000</v>
       </c>
       <c r="CB4" t="n">
-        <v>1742000000</v>
+        <v>1836800000</v>
       </c>
       <c r="CC4" t="n">
-        <v>355900000</v>
+        <v>354500000</v>
       </c>
       <c r="CD4" t="n">
-        <v>49700000</v>
+        <v>44800000</v>
       </c>
       <c r="CE4" t="n">
-        <v>306200000</v>
+        <v>309700000</v>
       </c>
       <c r="CF4" t="n">
-        <v>306200000</v>
+        <v>309700000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>96224</v>
+        <v>73876</v>
       </c>
       <c r="C5" t="n">
-        <v>131102423</v>
+        <v>131124771</v>
       </c>
       <c r="D5" t="n">
         <v>131198647</v>
       </c>
       <c r="E5" t="n">
-        <v>544500000</v>
+        <v>884100000</v>
       </c>
       <c r="F5" t="n">
-        <v>5005500000</v>
+        <v>7662400000</v>
       </c>
       <c r="G5" t="n">
-        <v>-533700000</v>
+        <v>374600000</v>
       </c>
       <c r="H5" t="n">
-        <v>6195200000</v>
+        <v>7860000000</v>
       </c>
       <c r="I5" t="n">
-        <v>-407400000</v>
+        <v>58800000</v>
       </c>
       <c r="J5" t="n">
-        <v>-533700000</v>
+        <v>374600000</v>
       </c>
       <c r="K5" t="n">
-        <v>3987300000</v>
+        <v>5991800000</v>
       </c>
       <c r="L5" t="n">
-        <v>5177000000</v>
+        <v>6189400000</v>
       </c>
       <c r="M5" t="n">
-        <v>6045300000</v>
+        <v>7191200000</v>
       </c>
       <c r="N5" t="n">
-        <v>5168700000</v>
+        <v>6207100000</v>
       </c>
       <c r="O5" t="n">
-        <v>-8300000</v>
+        <v>17700000</v>
       </c>
       <c r="P5" t="n">
-        <v>5177000000</v>
+        <v>6189400000</v>
       </c>
       <c r="Q5" t="n">
-        <v>1699200000</v>
+        <v>2135700000</v>
       </c>
       <c r="R5" t="n">
-        <v>3826400000</v>
+        <v>3826700000</v>
       </c>
       <c r="S5" t="n">
         <v>131100000</v>
@@ -2495,194 +2481,446 @@
         <v>131100000</v>
       </c>
       <c r="U5" t="n">
-        <v>10682200000</v>
+        <v>12598300000</v>
       </c>
       <c r="V5" t="n">
-        <v>5576900000</v>
+        <v>7088100000</v>
       </c>
       <c r="W5" t="n">
-        <v>200000</v>
+        <v>-100000</v>
       </c>
       <c r="X5" t="n">
-        <v>1400000</v>
+        <v>34900000</v>
       </c>
       <c r="Y5" t="n">
-        <v>1278600000</v>
+        <v>751800000</v>
       </c>
       <c r="Z5" t="n">
-        <v>184700000</v>
+        <v>200600000</v>
       </c>
       <c r="AA5" t="n">
-        <v>523500000</v>
+        <v>446700000</v>
       </c>
       <c r="AB5" t="n">
-        <v>3410800000</v>
+        <v>5433800000</v>
       </c>
       <c r="AC5" t="n">
-        <v>2542500000</v>
+        <v>4432000000</v>
       </c>
       <c r="AD5" t="n">
-        <v>868300000</v>
+        <v>1001800000</v>
       </c>
       <c r="AE5" t="n">
-        <v>143100000</v>
+        <v>213100000</v>
       </c>
       <c r="AF5" t="n">
-        <v>5105300000</v>
+        <v>5510200000</v>
       </c>
       <c r="AG5" t="n">
         <v>-100000</v>
       </c>
       <c r="AH5" t="n">
-        <v>1594700000</v>
+        <v>2228600000</v>
       </c>
       <c r="AI5" t="n">
-        <v>1444800000</v>
+        <v>1559800000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>149900000</v>
+        <v>668800000</v>
       </c>
       <c r="AK5" t="n">
-        <v>414600000</v>
+        <v>526300000</v>
       </c>
       <c r="AL5" t="n">
-        <v>197200000</v>
+        <v>269400000</v>
       </c>
       <c r="AM5" t="n">
-        <v>1613900000</v>
+        <v>1382100000</v>
       </c>
       <c r="AN5" t="n">
-        <v>5400000</v>
+        <v>11200000</v>
       </c>
       <c r="AO5" t="n">
-        <v>170200000</v>
+        <v>210500000</v>
       </c>
       <c r="AP5" t="n">
-        <v>1443700000</v>
+        <v>1160400000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>15850900000</v>
+        <v>18805400000</v>
       </c>
       <c r="AR5" t="n">
-        <v>11153000000</v>
+        <v>13236400000</v>
       </c>
       <c r="AS5" t="n">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="AT5" t="n">
-        <v>79700000</v>
+        <v>80600000</v>
       </c>
       <c r="AU5" t="n">
-        <v>449300000</v>
+        <v>489300000</v>
       </c>
       <c r="AV5" t="n">
-        <v>4200000</v>
+        <v>17600000</v>
       </c>
       <c r="AW5" t="n">
-        <v>74400000</v>
+        <v>176600000</v>
       </c>
       <c r="AX5" t="n">
-        <v>74400000</v>
+        <v>176600000</v>
       </c>
       <c r="AY5" t="n">
-        <v>108400000</v>
+        <v>130100000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>84300000</v>
+        <v>110300000</v>
       </c>
       <c r="BA5" t="n">
-        <v>24100000</v>
+        <v>19800000</v>
       </c>
       <c r="BB5" t="n">
-        <v>5710700000</v>
+        <v>5814800000</v>
       </c>
       <c r="BC5" t="n">
-        <v>2165900000</v>
+        <v>2166600000</v>
       </c>
       <c r="BD5" t="n">
-        <v>3544800000</v>
+        <v>3648200000</v>
       </c>
       <c r="BE5" t="n">
-        <v>3381800000</v>
+        <v>4422800000</v>
       </c>
       <c r="BF5" t="n">
-        <v>-2964200000</v>
+        <v>-3156800000</v>
       </c>
       <c r="BG5" t="n">
-        <v>6346000000</v>
+        <v>7579600000</v>
       </c>
       <c r="BH5" t="n">
-        <v>121700000</v>
+        <v>218400000</v>
       </c>
       <c r="BI5" t="n">
-        <v>4666600000</v>
-      </c>
-      <c r="BJ5" t="inlineStr"/>
+        <v>5404500000</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>1025600000</v>
+      </c>
       <c r="BK5" t="n">
-        <v>1557700000</v>
+        <v>931100000</v>
       </c>
       <c r="BL5" t="n">
         <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>4697900000</v>
+        <v>5569000000</v>
       </c>
       <c r="BN5" t="n">
-        <v>400000</v>
+        <v>-200000</v>
       </c>
       <c r="BO5" t="n">
-        <v>8900000</v>
+        <v>12700000</v>
       </c>
       <c r="BP5" t="n">
         <v>0</v>
       </c>
       <c r="BQ5" t="n">
-        <v>48100000</v>
+        <v>82600000</v>
       </c>
       <c r="BR5" t="n">
+        <v>500000</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>54100000</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>1694600000</v>
+      </c>
+      <c r="BU5" t="n">
+        <v>945700000</v>
+      </c>
+      <c r="BV5" t="n">
+        <v>294300000</v>
+      </c>
+      <c r="BW5" t="n">
+        <v>454600000</v>
+      </c>
+      <c r="BX5" t="n">
+        <v>288300000</v>
+      </c>
+      <c r="BY5" t="n">
+        <v>177200000</v>
+      </c>
+      <c r="BZ5" t="n">
+        <v>1695600000</v>
+      </c>
+      <c r="CA5" t="n">
+        <v>-90100000</v>
+      </c>
+      <c r="CB5" t="n">
+        <v>1785700000</v>
+      </c>
+      <c r="CC5" t="n">
+        <v>839800000</v>
+      </c>
+      <c r="CD5" t="n">
+        <v>53300000</v>
+      </c>
+      <c r="CE5" t="n">
+        <v>786500000</v>
+      </c>
+      <c r="CF5" t="n">
+        <v>786500000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>73876</v>
+      </c>
+      <c r="C6" t="n">
+        <v>131124771</v>
+      </c>
+      <c r="D6" t="n">
+        <v>131198647</v>
+      </c>
+      <c r="E6" t="n">
+        <v>542500000</v>
+      </c>
+      <c r="F6" t="n">
+        <v>7419700000</v>
+      </c>
+      <c r="G6" t="n">
+        <v>624400000</v>
+      </c>
+      <c r="H6" t="n">
+        <v>7114400000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-26000000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>624400000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>6403000000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>6097700000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>7000700000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>6122800000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>25100000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>6097700000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>2268900000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>3826700000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>131100000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>131100000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>12172100000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>7065300000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>100000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>24800000</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>607600000</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>199700000</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>388000000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>5560700000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>4657700000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>903000000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>275000000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>5106800000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>-100000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>1859000000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1745300000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>113700000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>539400000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>335500000</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1436800000</v>
+      </c>
+      <c r="AN6" t="n">
         <v>9300000</v>
       </c>
-      <c r="BS5" t="n">
-        <v>65200000</v>
-      </c>
-      <c r="BT5" t="n">
-        <v>1566800000</v>
-      </c>
-      <c r="BU5" t="n">
-        <v>761600000</v>
-      </c>
-      <c r="BV5" t="n">
-        <v>363200000</v>
-      </c>
-      <c r="BW5" t="n">
-        <v>442000000</v>
-      </c>
-      <c r="BX5" t="n">
-        <v>529100000</v>
-      </c>
-      <c r="BY5" t="n">
-        <v>148200000</v>
-      </c>
-      <c r="BZ5" t="n">
-        <v>1339200000</v>
-      </c>
-      <c r="CA5" t="n">
-        <v>-57300000</v>
-      </c>
-      <c r="CB5" t="n">
-        <v>1396500000</v>
-      </c>
-      <c r="CC5" t="n">
-        <v>517600000</v>
-      </c>
-      <c r="CD5" t="n">
-        <v>43900000</v>
-      </c>
-      <c r="CE5" t="n">
-        <v>473700000</v>
-      </c>
-      <c r="CF5" t="n">
-        <v>473700000</v>
+      <c r="AO6" t="n">
+        <v>172100000</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1255400000</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>18294900000</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>13214100000</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>-1200000</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>76900000</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>440900000</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>7800000</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>168300000</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>168300000</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>134700000</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>113000000</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>21700000</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>5473300000</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>2022400000</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>3450900000</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>4543800000</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>-3334200000</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>7878000000</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>149100000</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>5658200000</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>1091400000</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>979300000</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>5080800000</v>
+      </c>
+      <c r="BN6" t="inlineStr"/>
+      <c r="BO6" t="n">
+        <v>35100000</v>
+      </c>
+      <c r="BP6" t="inlineStr"/>
+      <c r="BQ6" t="n">
+        <v>86000000</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>700000</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>56700000</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>1575000000</v>
+      </c>
+      <c r="BU6" t="n">
+        <v>906100000</v>
+      </c>
+      <c r="BV6" t="n">
+        <v>285200000</v>
+      </c>
+      <c r="BW6" t="n">
+        <v>383700000</v>
+      </c>
+      <c r="BX6" t="n">
+        <v>271100000</v>
+      </c>
+      <c r="BY6" t="n">
+        <v>216200000</v>
+      </c>
+      <c r="BZ6" t="n">
+        <v>1528300000</v>
+      </c>
+      <c r="CA6" t="n">
+        <v>-93600000</v>
+      </c>
+      <c r="CB6" t="n">
+        <v>1621900000</v>
+      </c>
+      <c r="CC6" t="n">
+        <v>524600000</v>
+      </c>
+      <c r="CD6" t="n">
+        <v>50400000</v>
+      </c>
+      <c r="CE6" t="n">
+        <v>474200000</v>
+      </c>
+      <c r="CF6" t="n">
+        <v>474200000</v>
       </c>
     </row>
   </sheetData>
@@ -2696,7 +2934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO5"/>
+  <dimension ref="A1:AO6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2903,476 +3141,527 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
-      </c>
-      <c r="B2" t="n">
-        <v>1170600000</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-845700000</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1016600000</v>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="n">
-        <v>787000000</v>
-      </c>
+        <v>44561</v>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="n">
+        <v>-333800000</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="n">
-        <v>311800000</v>
-      </c>
-      <c r="I2" t="n">
-        <v>-2100000</v>
-      </c>
-      <c r="J2" t="n">
-        <v>477300000</v>
-      </c>
-      <c r="K2" t="n">
-        <v>-224700000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-50400000</v>
-      </c>
-      <c r="M2" t="n">
-        <v>-103900000</v>
-      </c>
-      <c r="N2" t="n">
-        <v>-91800000</v>
-      </c>
-      <c r="O2" t="n">
-        <v>-91800000</v>
-      </c>
-      <c r="P2" t="n">
-        <v>170900000</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>170900000</v>
-      </c>
-      <c r="R2" t="n">
-        <v>-845700000</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1016600000</v>
-      </c>
-      <c r="T2" t="n">
-        <v>-468600000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>-453800000</v>
-      </c>
-      <c r="V2" t="n">
-        <v>11600000</v>
-      </c>
-      <c r="W2" t="n">
-        <v>-26400000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>10300000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>-36700000</v>
-      </c>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="n">
-        <v>1170600000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-302900000</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>140200000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>-226600000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>243000000</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>149200000</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>93800000</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>-529400000</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>19300000</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1139200000</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>546300000</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>592900000</v>
-      </c>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="n">
-        <v>-5600000</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>777800000</v>
-      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="n">
+        <v>-333800000</v>
+      </c>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
+      <c r="AJ2" t="inlineStr"/>
+      <c r="AK2" t="inlineStr"/>
+      <c r="AL2" t="inlineStr"/>
+      <c r="AM2" t="n">
+        <v>-31200000</v>
+      </c>
+      <c r="AN2" t="inlineStr"/>
+      <c r="AO2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>1144000000</v>
+        <v>-345900000</v>
       </c>
       <c r="C3" t="n">
-        <v>-1621700000</v>
+        <v>-1757300000</v>
       </c>
       <c r="D3" t="n">
-        <v>1147500000</v>
+        <v>2699700000</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
-        <v>311800000</v>
+        <v>332200000</v>
       </c>
       <c r="G3" t="n">
-        <v>5200000</v>
+        <v>-100000</v>
       </c>
       <c r="H3" t="n">
-        <v>318100000</v>
+        <v>483000000</v>
       </c>
       <c r="I3" t="n">
-        <v>-5000000</v>
+        <v>2100000</v>
       </c>
       <c r="J3" t="n">
-        <v>-6500000</v>
+        <v>-152800000</v>
       </c>
       <c r="K3" t="n">
-        <v>-721700000</v>
+        <v>562800000</v>
       </c>
       <c r="L3" t="n">
-        <v>14000000</v>
+        <v>7100000</v>
       </c>
       <c r="M3" t="n">
-        <v>-99200000</v>
+        <v>-51900000</v>
       </c>
       <c r="N3" t="n">
-        <v>-24900000</v>
+        <v>-196700000</v>
       </c>
       <c r="O3" t="n">
-        <v>-24900000</v>
+        <v>-196700000</v>
       </c>
       <c r="P3" t="n">
-        <v>-474200000</v>
+        <v>942400000</v>
       </c>
       <c r="Q3" t="n">
-        <v>-474200000</v>
+        <v>942400000</v>
       </c>
       <c r="R3" t="n">
-        <v>-1621700000</v>
+        <v>-1757300000</v>
       </c>
       <c r="S3" t="n">
-        <v>1147500000</v>
+        <v>2699700000</v>
       </c>
       <c r="T3" t="n">
-        <v>-428800000</v>
+        <v>-369700000</v>
       </c>
       <c r="U3" t="n">
-        <v>-435900000</v>
+        <v>-375300000</v>
       </c>
       <c r="V3" t="n">
-        <v>9900000</v>
+        <v>10500000</v>
       </c>
       <c r="W3" t="n">
-        <v>-2800000</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
+        <v>-4900000</v>
+      </c>
+      <c r="X3" t="inlineStr"/>
       <c r="Y3" t="n">
-        <v>-2800000</v>
+        <v>-4900000</v>
       </c>
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="n">
-        <v>1144000000</v>
+        <v>-345900000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-180000000</v>
+        <v>-160000000</v>
       </c>
       <c r="AC3" t="n">
-        <v>102000000</v>
+        <v>80600000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-162900000</v>
+        <v>-69900000</v>
       </c>
       <c r="AE3" t="n">
-        <v>27400000</v>
+        <v>-804400000</v>
       </c>
       <c r="AF3" t="n">
-        <v>59100000</v>
+        <v>-641200000</v>
       </c>
       <c r="AG3" t="n">
-        <v>-31700000</v>
+        <v>-163200000</v>
       </c>
       <c r="AH3" t="n">
-        <v>-345600000</v>
+        <v>-584200000</v>
       </c>
       <c r="AI3" t="n">
-        <v>81100000</v>
+        <v>30900000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1053000000</v>
+        <v>1033500000</v>
       </c>
       <c r="AK3" t="n">
-        <v>485500000</v>
+        <v>469700000</v>
       </c>
       <c r="AL3" t="n">
-        <v>567500000</v>
+        <v>563800000</v>
       </c>
       <c r="AM3" t="n">
-        <v>-85900000</v>
+        <v>-35500000</v>
       </c>
       <c r="AN3" t="n">
-        <v>-5900000</v>
+        <v>-4900000</v>
       </c>
       <c r="AO3" t="n">
-        <v>660600000</v>
+        <v>168300000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-345900000</v>
+        <v>1144000000</v>
       </c>
       <c r="C4" t="n">
-        <v>-1757300000</v>
+        <v>-1621700000</v>
       </c>
       <c r="D4" t="n">
-        <v>2699700000</v>
+        <v>1147500000</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
-        <v>332200000</v>
+        <v>311800000</v>
       </c>
       <c r="G4" t="n">
-        <v>-100000</v>
+        <v>5200000</v>
       </c>
       <c r="H4" t="n">
-        <v>483000000</v>
+        <v>318100000</v>
       </c>
       <c r="I4" t="n">
-        <v>2100000</v>
+        <v>-5000000</v>
       </c>
       <c r="J4" t="n">
-        <v>-152800000</v>
+        <v>-6500000</v>
       </c>
       <c r="K4" t="n">
-        <v>562800000</v>
+        <v>-721700000</v>
       </c>
       <c r="L4" t="n">
-        <v>7100000</v>
+        <v>14000000</v>
       </c>
       <c r="M4" t="n">
-        <v>-51900000</v>
+        <v>-99200000</v>
       </c>
       <c r="N4" t="n">
-        <v>-196700000</v>
+        <v>-24900000</v>
       </c>
       <c r="O4" t="n">
-        <v>-196700000</v>
+        <v>-24900000</v>
       </c>
       <c r="P4" t="n">
-        <v>942400000</v>
+        <v>-474200000</v>
       </c>
       <c r="Q4" t="n">
-        <v>942400000</v>
+        <v>-474200000</v>
       </c>
       <c r="R4" t="n">
-        <v>-1757300000</v>
+        <v>-1621700000</v>
       </c>
       <c r="S4" t="n">
-        <v>2699700000</v>
+        <v>1147500000</v>
       </c>
       <c r="T4" t="n">
-        <v>-369700000</v>
+        <v>-428800000</v>
       </c>
       <c r="U4" t="n">
-        <v>-375300000</v>
+        <v>-435900000</v>
       </c>
       <c r="V4" t="n">
-        <v>10500000</v>
+        <v>9900000</v>
       </c>
       <c r="W4" t="n">
-        <v>-4900000</v>
-      </c>
-      <c r="X4" t="inlineStr"/>
+        <v>-2800000</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
       <c r="Y4" t="n">
-        <v>-4900000</v>
+        <v>-2800000</v>
       </c>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="n">
-        <v>-345900000</v>
+        <v>1144000000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-160000000</v>
+        <v>-180000000</v>
       </c>
       <c r="AC4" t="n">
-        <v>80600000</v>
+        <v>102000000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-69900000</v>
+        <v>-162900000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-804400000</v>
+        <v>27400000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-641200000</v>
+        <v>59100000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-163200000</v>
+        <v>-31700000</v>
       </c>
       <c r="AH4" t="n">
-        <v>-584200000</v>
+        <v>-345600000</v>
       </c>
       <c r="AI4" t="n">
-        <v>30900000</v>
+        <v>81100000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>1033500000</v>
+        <v>1053000000</v>
       </c>
       <c r="AK4" t="n">
-        <v>469700000</v>
+        <v>485500000</v>
       </c>
       <c r="AL4" t="n">
-        <v>563800000</v>
+        <v>567500000</v>
       </c>
       <c r="AM4" t="n">
-        <v>-35500000</v>
+        <v>-85900000</v>
       </c>
       <c r="AN4" t="n">
-        <v>-4900000</v>
+        <v>-5900000</v>
       </c>
       <c r="AO4" t="n">
-        <v>168300000</v>
+        <v>660600000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>881700000</v>
+        <v>1170600000</v>
       </c>
       <c r="C5" t="n">
-        <v>-772700000</v>
+        <v>-845700000</v>
       </c>
       <c r="D5" t="n">
-        <v>623900000</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-333800000</v>
-      </c>
+        <v>1016600000</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
-        <v>483000000</v>
+        <v>787000000</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>314400000</v>
+        <v>311800000</v>
       </c>
       <c r="I5" t="n">
-        <v>10800000</v>
+        <v>-2100000</v>
       </c>
       <c r="J5" t="n">
-        <v>157800000</v>
+        <v>477300000</v>
       </c>
       <c r="K5" t="n">
-        <v>-386100000</v>
+        <v>-224700000</v>
       </c>
       <c r="L5" t="n">
-        <v>2300000</v>
+        <v>-57400000</v>
       </c>
       <c r="M5" t="n">
-        <v>-182200000</v>
+        <v>-96900000</v>
       </c>
       <c r="N5" t="n">
-        <v>-53700000</v>
+        <v>-91800000</v>
       </c>
       <c r="O5" t="n">
-        <v>-53700000</v>
+        <v>-91800000</v>
       </c>
       <c r="P5" t="n">
-        <v>-148800000</v>
+        <v>170900000</v>
       </c>
       <c r="Q5" t="n">
-        <v>-148800000</v>
+        <v>170900000</v>
       </c>
       <c r="R5" t="n">
-        <v>-772700000</v>
+        <v>-845700000</v>
       </c>
       <c r="S5" t="n">
-        <v>623900000</v>
+        <v>1016600000</v>
       </c>
       <c r="T5" t="n">
-        <v>-337800000</v>
+        <v>-468600000</v>
       </c>
       <c r="U5" t="n">
-        <v>-329000000</v>
+        <v>-453800000</v>
       </c>
       <c r="V5" t="n">
-        <v>8200000</v>
+        <v>11600000</v>
       </c>
       <c r="W5" t="n">
-        <v>-17000000</v>
-      </c>
-      <c r="X5" t="inlineStr"/>
+        <v>-26400000</v>
+      </c>
+      <c r="X5" t="n">
+        <v>10300000</v>
+      </c>
       <c r="Y5" t="n">
-        <v>-17000000</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>-333800000</v>
-      </c>
+        <v>-36700000</v>
+      </c>
+      <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="n">
-        <v>881700000</v>
+        <v>1170600000</v>
       </c>
       <c r="AB5" t="n">
-        <v>-201400000</v>
-      </c>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
+        <v>-302900000</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>140200000</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>-226600000</v>
+      </c>
       <c r="AE5" t="n">
-        <v>-201900000</v>
+        <v>243000000</v>
       </c>
       <c r="AF5" t="n">
-        <v>288200000</v>
+        <v>149200000</v>
       </c>
       <c r="AG5" t="n">
-        <v>-490100000</v>
+        <v>93800000</v>
       </c>
       <c r="AH5" t="n">
-        <v>-450800000</v>
+        <v>-529400000</v>
       </c>
       <c r="AI5" t="n">
-        <v>36600000</v>
+        <v>19300000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>940900000</v>
+        <v>1139200000</v>
       </c>
       <c r="AK5" t="n">
-        <v>415200000</v>
+        <v>546300000</v>
       </c>
       <c r="AL5" t="n">
-        <v>525700000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>-31200000</v>
-      </c>
+        <v>592900000</v>
+      </c>
+      <c r="AM5" t="inlineStr"/>
       <c r="AN5" t="n">
-        <v>-5300000</v>
+        <v>-5600000</v>
       </c>
       <c r="AO5" t="n">
-        <v>794800000</v>
+        <v>777800000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1131800000</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-829600000</v>
+      </c>
+      <c r="D6" t="n">
+        <v>192200000</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>474900000</v>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>787000000</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-9800000</v>
+      </c>
+      <c r="J6" t="n">
+        <v>-302300000</v>
+      </c>
+      <c r="K6" t="n">
+        <v>-1011800000</v>
+      </c>
+      <c r="L6" t="n">
+        <v>16800000</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-93500000</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-107500000</v>
+      </c>
+      <c r="O6" t="n">
+        <v>-107500000</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-637400000</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-637400000</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-829600000</v>
+      </c>
+      <c r="S6" t="n">
+        <v>192200000</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-422300000</v>
+      </c>
+      <c r="U6" t="n">
+        <v>-400700000</v>
+      </c>
+      <c r="V6" t="n">
+        <v>13000000</v>
+      </c>
+      <c r="W6" t="n">
+        <v>-34600000</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>-34600000</v>
+      </c>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="n">
+        <v>1131800000</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>-250500000</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>172400000</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>-213500000</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>257800000</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>180300000</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>77500000</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>-579800000</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>146000000</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>1199700000</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>588500000</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>611200000</v>
+      </c>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="n">
+        <v>-13500000</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>500900000</v>
       </c>
     </row>
   </sheetData>
@@ -3942,197 +4231,197 @@
       </c>
       <c r="DG1" t="inlineStr">
         <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DN1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>earningsTimestamp</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>earningsCallTimestampStart</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>earningsCallTimestampEnd</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>isEarningsDateEstimate</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="EA1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="EB1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="EC1" t="inlineStr">
+      <c r="EL1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="EO1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="EP1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="EQ1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="ER1" t="inlineStr">
         <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="EG1" t="inlineStr">
+      <c r="ES1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="EQ1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="ER1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="ES1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
         </is>
       </c>
       <c r="ET1" t="inlineStr">
@@ -4152,10 +4441,8 @@
           <t>Frankfurt am Main</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>60549</t>
-        </is>
+      <c r="C2" t="n">
+        <v>60549</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -4236,7 +4523,7 @@
         <v>3</v>
       </c>
       <c r="V2" t="n">
-        <v>1780272000</v>
+        <v>1780531200</v>
       </c>
       <c r="W2" t="n">
         <v>1767139200</v>
@@ -4253,76 +4540,76 @@
         <v>2</v>
       </c>
       <c r="AA2" t="n">
-        <v>41.35</v>
+        <v>39.22</v>
       </c>
       <c r="AB2" t="n">
-        <v>43.42</v>
+        <v>38.91</v>
       </c>
       <c r="AC2" t="n">
-        <v>41.92</v>
+        <v>38.91</v>
       </c>
       <c r="AD2" t="n">
-        <v>43.42</v>
+        <v>39.12</v>
       </c>
       <c r="AE2" t="n">
-        <v>41.35</v>
+        <v>39.22</v>
       </c>
       <c r="AF2" t="n">
-        <v>43.42</v>
+        <v>38.91</v>
       </c>
       <c r="AG2" t="n">
-        <v>41.92</v>
+        <v>38.91</v>
       </c>
       <c r="AH2" t="n">
-        <v>43.42</v>
+        <v>39.12</v>
       </c>
       <c r="AI2" t="n">
         <v>0.62</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AK2" t="n">
         <v>1780012800</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.39419997</v>
+        <v>0.2929</v>
       </c>
       <c r="AM2" t="n">
-        <v>2.032</v>
+        <v>2.022</v>
       </c>
       <c r="AN2" t="n">
-        <v>20.471155</v>
+        <v>13.714287</v>
       </c>
       <c r="AO2" t="n">
-        <v>489</v>
+        <v>138</v>
       </c>
       <c r="AP2" t="n">
-        <v>489</v>
+        <v>138</v>
       </c>
       <c r="AQ2" t="n">
-        <v>158</v>
+        <v>233</v>
       </c>
       <c r="AR2" t="n">
-        <v>89</v>
+        <v>530</v>
       </c>
       <c r="AS2" t="n">
-        <v>89</v>
+        <v>530</v>
       </c>
       <c r="AT2" t="n">
-        <v>42.43</v>
+        <v>38.38</v>
       </c>
       <c r="AU2" t="n">
-        <v>42.71</v>
+        <v>38.53</v>
       </c>
       <c r="AV2" t="n">
-        <v>5583292928</v>
+        <v>5035191296</v>
       </c>
       <c r="AW2" t="n">
-        <v>5454790473</v>
+        <v>5111243573</v>
       </c>
       <c r="AX2" t="n">
-        <v>41.24</v>
+        <v>38.91</v>
       </c>
       <c r="AY2" t="n">
         <v>69.8</v>
@@ -4334,19 +4621,19 @@
         <v>28.88</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.49495086</v>
+        <v>0.44636244</v>
       </c>
       <c r="BC2" t="n">
-        <v>45.0572</v>
+        <v>44.6046</v>
       </c>
       <c r="BD2" t="n">
-        <v>56.1838</v>
+        <v>55.74915</v>
       </c>
       <c r="BE2" t="n">
         <v>0.62</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.014993954</v>
+        <v>0.01580826</v>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
@@ -4357,7 +4644,7 @@
         <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>12645738496</v>
+        <v>12205242368</v>
       </c>
       <c r="BJ2" t="n">
         <v>0.0326</v>
@@ -4372,7 +4659,7 @@
         <v>0.4652</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.38066003</v>
+        <v>0.36755002</v>
       </c>
       <c r="BO2" t="n">
         <v>131124771</v>
@@ -4381,7 +4668,7 @@
         <v>47.649</v>
       </c>
       <c r="BQ2" t="n">
-        <v>0.893618</v>
+        <v>0.8058932</v>
       </c>
       <c r="BR2" t="n">
         <v>1767139200</v>
@@ -4396,22 +4683,22 @@
         <v>367800000</v>
       </c>
       <c r="BV2" t="n">
-        <v>2.08</v>
+        <v>2.8</v>
       </c>
       <c r="BW2" t="n">
         <v>0.33</v>
       </c>
       <c r="BX2" t="n">
-        <v>1.121</v>
+        <v>1.082</v>
       </c>
       <c r="BY2" t="n">
-        <v>7.552</v>
+        <v>7.289</v>
       </c>
       <c r="BZ2" t="n">
-        <v>-0.0026531816</v>
+        <v>-0.07701099</v>
       </c>
       <c r="CA2" t="n">
-        <v>0.27449715</v>
+        <v>0.22635591</v>
       </c>
       <c r="CB2" t="n">
         <v>0.62</v>
@@ -4425,7 +4712,7 @@
         </is>
       </c>
       <c r="CE2" t="n">
-        <v>42.58</v>
+        <v>38.4</v>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
@@ -4524,144 +4811,144 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="DG2" t="n">
-        <v>1.2300034</v>
+      <c r="DG2" t="inlineStr">
+        <is>
+          <t>MIL</t>
+        </is>
       </c>
       <c r="DH2" t="inlineStr">
         <is>
-          <t>41.92 - 43.42</t>
+          <t>finmb_29228863</t>
         </is>
       </c>
       <c r="DI2" t="inlineStr">
         <is>
+          <t>Europe/Rome</t>
+        </is>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>CEST</t>
+        </is>
+      </c>
+      <c r="DK2" t="n">
+        <v>7200000</v>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
+          <t>it_market</t>
+        </is>
+      </c>
+      <c r="DM2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DN2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>1700812800000</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>-0.8199997</v>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>38.91 - 39.12</t>
+        </is>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
           <t>Milan</t>
         </is>
       </c>
-      <c r="DJ2" t="n">
-        <v>158</v>
-      </c>
-      <c r="DK2" t="n">
-        <v>1.3400002</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>0.032492727</v>
-      </c>
-      <c r="DM2" t="inlineStr">
-        <is>
-          <t>41.24 - 69.8</t>
-        </is>
-      </c>
-      <c r="DN2" t="n">
-        <v>-27.220001</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>-0.38997135</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>-0.26531816</v>
-      </c>
-      <c r="DQ2" t="n">
+      <c r="DS2" t="n">
+        <v>233</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>-0.5099983</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>-0.0131071275</v>
+      </c>
+      <c r="DV2" t="inlineStr">
+        <is>
+          <t>38.91 - 69.8</t>
+        </is>
+      </c>
+      <c r="DW2" t="n">
+        <v>-31.400002</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>-0.44985673</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>-7.701099</v>
+      </c>
+      <c r="DZ2" t="n">
         <v>1785425400</v>
       </c>
-      <c r="DR2" t="n">
+      <c r="EA2" t="n">
         <v>1785425400</v>
       </c>
-      <c r="DS2" t="n">
+      <c r="EB2" t="n">
         <v>1785425400</v>
       </c>
-      <c r="DT2" t="n">
+      <c r="EC2" t="n">
         <v>1761821940</v>
       </c>
-      <c r="DU2" t="n">
+      <c r="ED2" t="n">
         <v>1761821940</v>
       </c>
-      <c r="DV2" t="b">
+      <c r="EE2" t="b">
         <v>0</v>
       </c>
-      <c r="DW2" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>-2.4771996</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>-0.054978993</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>-13.603798</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>-0.24213026</v>
-      </c>
-      <c r="EB2" t="n">
+      <c r="EF2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>-6.2045975</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>-0.13910219</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>-17.349148</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>-0.31120023</v>
+      </c>
+      <c r="EK2" t="n">
         <v>20</v>
       </c>
-      <c r="EC2" t="n">
+      <c r="EL2" t="n">
         <v>15</v>
       </c>
-      <c r="ED2" t="b">
+      <c r="EM2" t="b">
         <v>0</v>
       </c>
-      <c r="EE2" t="n">
-        <v>1700812800000</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>2.9746153</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>42.58</v>
-      </c>
-      <c r="EH2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EI2" t="inlineStr">
+      <c r="EN2" t="inlineStr">
+        <is>
+          <t>KION GROUP</t>
+        </is>
+      </c>
+      <c r="EO2" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="EJ2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="EK2" t="inlineStr">
-        <is>
-          <t>KION GROUP</t>
-        </is>
-      </c>
-      <c r="EL2" t="n">
-        <v>1780323403</v>
-      </c>
-      <c r="EM2" t="inlineStr">
-        <is>
-          <t>MIL</t>
-        </is>
-      </c>
-      <c r="EN2" t="inlineStr">
-        <is>
-          <t>finmb_29228863</t>
-        </is>
-      </c>
-      <c r="EO2" t="inlineStr">
-        <is>
-          <t>Europe/Rome</t>
-        </is>
-      </c>
-      <c r="EP2" t="inlineStr">
-        <is>
-          <t>CEST</t>
-        </is>
-      </c>
-      <c r="EQ2" t="n">
-        <v>7200000</v>
-      </c>
-      <c r="ER2" t="inlineStr">
-        <is>
-          <t>it_market</t>
-        </is>
-      </c>
-      <c r="ES2" t="b">
-        <v>0</v>
+      <c r="EP2" t="n">
+        <v>1780997341</v>
+      </c>
+      <c r="EQ2" t="inlineStr">
+        <is>
+          <t>POSTPOST</t>
+        </is>
+      </c>
+      <c r="ER2" t="n">
+        <v>-2.0907693</v>
+      </c>
+      <c r="ES2" t="n">
+        <v>38.4</v>
       </c>
       <c r="ET2" t="inlineStr"/>
     </row>
